--- a/teacher/tracker-as-pure.xlsx
+++ b/teacher/tracker-as-pure.xlsx
@@ -159,7 +159,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
     <dxf>
       <font>
         <b val="1"/>
@@ -190,6 +190,42 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="001B998B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC0392B"/>
+          <bgColor rgb="FFC0392B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4A93F"/>
+          <bgColor rgb="FFF4A93F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1B998B"/>
+          <bgColor rgb="FF1B998B"/>
         </patternFill>
       </fill>
     </dxf>
@@ -843,7 +879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1200,13 +1236,13 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:G27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1225,7 +1261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1552,13 +1588,13 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:F27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1577,7 +1613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1904,13 +1940,13 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:F27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1929,7 +1965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2346,13 +2382,13 @@
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:I27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2371,7 +2407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2728,13 +2764,13 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:G27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2753,7 +2789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3110,13 +3146,13 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:G27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3135,7 +3171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3492,13 +3528,13 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:G27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3517,7 +3553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3844,13 +3880,13 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:F27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3869,7 +3905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4226,13 +4262,13 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:G27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4251,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4638,13 +4674,13 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:H27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4663,7 +4699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4990,13 +5026,13 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:F27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5015,7 +5051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5342,13 +5378,13 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:F27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5367,7 +5403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5664,13 +5700,13 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:E27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5689,7 +5725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6016,13 +6052,13 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:F27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
